--- a/data/export/2026-10-21-浦东78路.xlsx
+++ b/data/export/2026-10-21-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,36 +632,32 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -669,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -693,37 +689,33 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -834,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -842,22 +834,22 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>06:40</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -890,12 +882,12 @@
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -945,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -953,7 +945,7 @@
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -963,7 +955,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1001,12 +993,12 @@
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1020,7 +1012,7 @@
       <c r="T5" s="2" t="inlineStr"/>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -1056,7 +1048,1339 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-浦东78路.xlsx
+++ b/data/export/2026-10-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,17 +693,17 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -709,13 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -776,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -815,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -826,7 +834,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -854,32 +862,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -887,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,33 +923,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -998,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1037,7 +1053,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1048,7 +1064,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1076,32 +1092,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1109,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1133,33 +1153,37 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1244,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1294,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1355,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1405,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1466,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1481,7 +1505,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1492,7 +1516,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1577,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1627,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1688,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1703,7 +1727,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1714,7 +1738,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1799,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1849,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1910,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1960,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2021,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2071,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2132,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2182,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2243,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2293,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2311,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2330,7 +2354,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2344,7 +2368,7 @@
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2374,13 +2398,1024 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr"/>
-      <c r="AC17" s="2" t="inlineStr">
-        <is>
-          <t>—/15</t>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-浦东78路.xlsx
+++ b/data/export/2026-10-21-浦东78路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">

--- a/data/export/2026-10-21-浦东78路.xlsx
+++ b/data/export/2026-10-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1655,32 +1655,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1688,7 +1692,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1712,17 +1716,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1732,13 +1736,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1766,32 +1774,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>111分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -1799,7 +1811,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1823,33 +1835,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>111.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1926,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1949,7 +1965,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -1988,32 +2004,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2021,7 +2041,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2045,33 +2065,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2156,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2210,32 +2234,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2243,7 +2271,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2267,33 +2295,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2321,32 +2353,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2354,7 +2390,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2378,17 +2414,17 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2398,17 +2434,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2505,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2580,7 +2616,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2619,7 +2655,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2691,7 +2727,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2745,7 +2781,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2842,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2917,7 +2953,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2956,7 +2992,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3028,7 +3064,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3143,7 +3179,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3182,7 +3218,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3201,22 +3237,22 @@
       <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3249,12 +3285,12 @@
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3312,7 +3348,7 @@
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3322,7 +3358,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3360,12 +3396,12 @@
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3379,7 +3415,7 @@
       <c r="T26" s="2" t="inlineStr"/>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3414,6 +3450,1132 @@
       </c>
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>111.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-21-浦东78路.xlsx
+++ b/data/export/2026-10-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,13 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,14 +942,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>93.0</t>
@@ -953,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1058,13 +1062,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1168,22 +1176,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1355,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1394,7 +1402,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1466,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1505,18 +1513,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1589,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1692,7 +1704,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1731,22 +1743,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1823,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1850,7 +1862,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1865,7 +1877,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1938,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2041,7 +2053,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2080,22 +2092,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2283,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2325,7 +2337,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2363,12 +2375,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
@@ -2390,7 +2402,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2439,12 +2451,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2472,32 +2484,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2505,7 +2521,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2529,17 +2545,17 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2549,13 +2565,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2636,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2694,32 +2714,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -2727,7 +2751,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2751,29 +2775,29 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>93.0</t>
@@ -2781,7 +2805,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2809,32 +2833,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
@@ -2842,7 +2870,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2866,17 +2894,17 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -2886,13 +2914,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2920,32 +2952,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2953,7 +2989,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2977,17 +3013,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -2997,13 +3033,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3031,32 +3071,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3064,7 +3108,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3088,37 +3132,37 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3146,32 +3190,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3179,7 +3227,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3203,17 +3251,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3223,13 +3271,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3342,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3368,32 +3420,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3401,7 +3457,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3425,33 +3481,37 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3512,7 +3572,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3551,7 +3611,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3590,32 +3650,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3623,7 +3687,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3647,37 +3711,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3802,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3816,32 +3880,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -3849,7 +3917,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3873,37 +3941,37 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3964,7 +4032,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4003,7 +4071,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4018,7 +4086,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4147,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4190,7 +4258,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4244,7 +4312,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4373,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4416,7 +4484,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4460,13 +4528,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB35" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4474,22 +4546,22 @@
       <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4522,12 +4594,12 @@
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4541,43 +4613,848 @@
       <c r="T36" s="2" t="inlineStr"/>
       <c r="U36" s="2" t="inlineStr">
         <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
           <t>10:20</t>
         </is>
       </c>
-      <c r="V36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W36" s="2" t="inlineStr">
+      <c r="W37" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X36" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y36" s="2" t="inlineStr">
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z36" s="2" t="inlineStr">
+      <c r="Z37" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr"/>
-      <c r="AC36" s="2" t="inlineStr">
+      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>111.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-浦东78路.xlsx
+++ b/data/export/2026-10-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC43"/>
+  <dimension ref="A1:AC49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,22 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1513,17 +1513,17 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1633,13 +1633,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1708,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1758,7 +1762,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1827,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1867,17 +1871,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1942,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1977,18 +1981,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2061,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2102,12 +2110,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2291,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2322,22 +2330,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2464,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2575,7 +2583,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2644,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2680,13 +2688,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2763,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2790,22 +2802,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2936,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2989,7 +3001,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3028,22 +3040,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3120,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3162,7 +3174,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3239,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3266,22 +3278,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3469,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3496,17 +3508,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3572,7 +3584,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3687,7 +3699,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3741,7 +3753,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3769,32 +3781,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3802,7 +3818,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3826,17 +3842,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3846,13 +3862,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3890,24 +3910,24 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3917,7 +3937,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3966,12 +3986,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3999,32 +4019,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -4032,7 +4056,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4056,17 +4080,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4076,17 +4100,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4114,32 +4138,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4147,7 +4175,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4171,33 +4199,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB32" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4225,32 +4257,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4258,7 +4294,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4282,37 +4318,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4340,32 +4376,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4373,7 +4413,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4397,17 +4437,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4417,13 +4457,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB34" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4451,32 +4495,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4484,7 +4532,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4508,37 +4556,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4566,32 +4614,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4599,7 +4651,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4623,37 +4675,37 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4766,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4768,7 +4820,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4796,32 +4848,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4829,7 +4885,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4853,37 +4909,37 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4911,32 +4967,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4944,7 +5004,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4968,32 +5028,32 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5059,7 +5119,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5170,7 +5230,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5224,7 +5284,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5285,7 +5345,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5334,12 +5394,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5460,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5444,17 +5504,707 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB43" s="2" t="inlineStr">
-        <is>
-          <t>111.0</t>
-        </is>
-      </c>
-      <c r="AC43" s="2" t="inlineStr">
-        <is>
-          <t>12/18</t>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-浦东78路.xlsx
+++ b/data/export/2026-10-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC49"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1402,18 +1402,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1528,7 +1532,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1647,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1766,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1866,22 +1870,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1946,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1981,22 +1985,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2065,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2100,7 +2104,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2115,7 +2119,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2295,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2330,7 +2334,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2345,7 +2349,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2468,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2587,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2702,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2767,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2817,7 +2821,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2940,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3005,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3055,7 +3059,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3178,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3243,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3288,12 +3292,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3473,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3523,7 +3527,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3588,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3623,18 +3627,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3761,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3872,7 +3880,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3945,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3976,7 +3984,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -3991,7 +3999,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4064,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4095,22 +4103,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4183,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4214,22 +4222,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4302,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4333,7 +4341,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4348,7 +4356,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4475,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4532,7 +4540,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4586,7 +4594,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4659,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4705,7 +4713,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4820,7 +4828,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4858,24 +4866,24 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4885,7 +4893,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4934,12 +4942,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5012,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5058,7 +5066,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5086,32 +5094,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5119,7 +5131,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5143,33 +5155,37 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB40" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -5284,7 +5300,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5345,7 +5361,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5384,7 +5400,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5399,7 +5415,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5427,32 +5443,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5460,7 +5480,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5484,37 +5504,37 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5575,7 +5595,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5614,7 +5634,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5629,7 +5649,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5657,32 +5677,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5690,7 +5714,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5714,37 +5738,37 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5805,7 +5829,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5859,7 +5883,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5920,7 +5944,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5974,7 +5998,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6035,7 +6059,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6084,12 +6108,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6150,7 +6174,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6204,7 +6228,582 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
           <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>89.7</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-浦东78路.xlsx
+++ b/data/export/2026-10-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,17 +1057,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2339,17 +2339,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2806,22 +2806,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3044,22 +3044,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3282,17 +3282,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4346,17 +4346,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4579,22 +4579,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4698,22 +4698,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4828,7 +4828,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4893,7 +4893,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4932,17 +4932,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5562,32 +5562,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5595,7 +5599,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5619,17 +5623,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5639,17 +5643,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5687,24 +5691,24 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5714,7 +5718,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5763,12 +5767,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5796,32 +5800,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5829,7 +5837,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5853,37 +5861,37 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5911,32 +5919,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5944,7 +5956,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5968,37 +5980,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6026,32 +6038,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6059,7 +6075,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6083,32 +6099,32 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6174,7 +6190,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6213,7 +6229,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6228,7 +6244,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6289,7 +6305,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6404,7 +6420,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6458,7 +6474,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6519,7 +6535,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6573,7 +6589,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6650,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6678,17 +6694,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6765,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6798,12 +6814,587 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>84.8</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>80.3</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
           <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-浦东78路.xlsx
+++ b/data/export/2026-10-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1402,17 +1402,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1522,17 +1522,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1875,17 +1875,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2104,22 +2104,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3517,17 +3517,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3627,17 +3627,17 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3984,22 +3984,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4108,17 +4108,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4828,7 +4828,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4893,7 +4893,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5056,17 +5056,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5170,17 +5170,17 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5400,22 +5400,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5524,17 +5524,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5837,7 +5837,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6048,24 +6048,24 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6157,32 +6157,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6190,7 +6194,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6214,17 +6218,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6234,17 +6238,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6272,32 +6276,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6305,7 +6313,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6329,32 +6337,32 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6387,32 +6395,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6420,7 +6432,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6444,37 +6456,37 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6502,32 +6514,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6535,7 +6551,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6559,17 +6575,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6579,17 +6595,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6666,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6704,7 +6720,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6765,7 +6781,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6819,7 +6835,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6896,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6934,7 +6950,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6995,7 +7011,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7049,7 +7065,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7110,7 +7126,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7159,7 +7175,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7225,7 +7241,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7269,17 +7285,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7340,7 +7356,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7398,6 +7414,236 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-21-浦东78路.xlsx
+++ b/data/export/2026-10-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1870,22 +1870,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1990,17 +1990,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2339,17 +2339,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4103,22 +4103,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4227,17 +4227,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4346,17 +4346,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4893,7 +4893,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5519,22 +5519,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5643,17 +5643,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5762,17 +5762,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5837,7 +5837,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6405,24 +6405,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6524,12 +6524,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6590,22 +6590,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6633,32 +6633,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6666,7 +6670,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6690,17 +6694,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6710,17 +6714,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6748,32 +6752,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6781,7 +6789,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6805,17 +6813,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6825,17 +6833,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6896,7 +6904,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7011,7 +7019,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7126,7 +7134,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7241,7 +7249,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7356,7 +7364,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7471,7 +7479,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7586,7 +7594,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7635,12 +7643,238 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-浦东78路.xlsx
+++ b/data/export/2026-10-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -449,7 +449,7 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,17 +823,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1522,12 +1522,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2334,17 +2334,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3287,12 +3287,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4341,17 +4341,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4579,17 +4579,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq26推进至seq35，推进9站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4782,10 +4782,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q37" s="2" t="inlineStr"/>
-      <c r="R37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>五莲路东陆路</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="S37" s="2" t="inlineStr"/>
-      <c r="T37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq18映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
           <t>10:20</t>
@@ -4813,7 +4825,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4893,7 +4905,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4937,12 +4949,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5012,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5056,12 +5068,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5131,7 +5143,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5213,12 +5225,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq26推进至seq30，推进4站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -5246,7 +5258,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5254,10 +5266,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q41" s="2" t="inlineStr"/>
-      <c r="R41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>张杨北路博兴路</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="S41" s="2" t="inlineStr"/>
-      <c r="T41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq15映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
           <t>10:45</t>
@@ -5285,7 +5309,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5361,7 +5385,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5480,7 +5504,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5599,7 +5623,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5638,17 +5662,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5718,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5757,7 +5781,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5767,7 +5791,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5837,7 +5861,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5876,17 +5900,17 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5956,7 +5980,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5995,7 +6019,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6075,7 +6099,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6119,12 +6143,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6194,7 +6218,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6238,12 +6262,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6313,7 +6337,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6432,7 +6456,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6551,7 +6575,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6643,12 +6667,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
@@ -6670,7 +6694,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6709,17 +6733,17 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6762,24 +6786,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6789,7 +6813,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6828,7 +6852,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6838,7 +6862,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6871,32 +6895,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6904,7 +6932,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6928,32 +6956,32 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7019,7 +7047,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7058,7 +7086,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7101,32 +7129,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7134,7 +7166,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7158,17 +7190,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7178,12 +7210,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7216,32 +7248,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7249,7 +7285,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7273,17 +7309,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7293,12 +7329,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7364,7 +7400,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7479,7 +7515,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7594,7 +7630,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7709,7 +7745,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7824,7 +7860,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7878,6 +7914,1152 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>84.8</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-21-浦东78路.xlsx
+++ b/data/export/2026-10-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC73"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1291,18 +1291,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1402,7 +1406,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1478,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1517,7 +1521,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1527,7 +1531,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1593,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1647,7 +1651,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1766,7 +1770,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1870,22 +1874,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2000,7 +2004,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2104,22 +2108,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2184,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2219,18 +2223,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2334,22 +2342,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2453,22 +2461,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2587,7 +2595,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2702,7 +2710,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2821,7 +2829,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2948,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3013,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3059,7 +3067,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3178,7 +3186,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3251,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3282,7 +3290,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3297,7 +3305,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3397,18 +3405,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3485,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3512,7 +3524,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3522,7 +3534,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3588,7 +3600,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3627,7 +3639,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3707,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3761,7 +3773,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3880,7 +3892,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3945,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3984,22 +3996,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4103,22 +4115,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4237,7 +4249,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4341,22 +4353,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4475,7 +4487,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4594,7 +4606,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4713,7 +4725,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4840,7 +4852,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4944,7 +4956,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4959,7 +4971,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5063,7 +5075,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5073,7 +5085,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5143,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5182,7 +5194,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5230,7 +5242,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq26推进至seq30，推进4站，达到≥2站确认条件</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq26推进至seq34，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -5258,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5324,7 +5336,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5424,22 +5436,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5543,22 +5555,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5662,22 +5674,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5796,7 +5808,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5915,7 +5927,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6034,7 +6046,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6138,7 +6150,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6153,7 +6165,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6257,7 +6269,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6267,7 +6279,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6337,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6376,7 +6388,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6456,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6495,22 +6507,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6575,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6614,22 +6626,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6733,22 +6745,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6867,7 +6879,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6986,7 +6998,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7047,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7101,7 +7113,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7205,7 +7217,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7220,7 +7232,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7258,12 +7270,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
@@ -7285,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7324,7 +7336,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7334,7 +7346,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7367,32 +7379,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7400,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7424,37 +7440,37 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -7515,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7554,7 +7570,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7597,32 +7613,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7630,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7654,37 +7674,37 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7712,32 +7732,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7745,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7769,37 +7793,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7827,32 +7851,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -7860,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7884,33 +7912,37 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB63" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7938,32 +7970,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -7971,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7995,33 +8031,37 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB64" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8049,32 +8089,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8082,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8106,37 +8150,37 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8197,7 +8241,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8251,7 +8295,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8312,7 +8356,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8366,7 +8410,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8427,7 +8471,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8481,7 +8525,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8586,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8596,7 +8640,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8657,7 +8701,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8711,7 +8755,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8772,7 +8816,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8826,7 +8870,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8887,7 +8931,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8941,7 +8985,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9046,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9056,7 +9100,1042 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>79.2</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>85.2</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>86.2</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>85.8</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-浦东78路.xlsx
+++ b/data/export/2026-10-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1062,17 +1062,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,22 +1176,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1521,22 +1521,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1636,22 +1636,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1755,22 +1755,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2695,22 +2695,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2814,22 +2814,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3052,22 +3052,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3171,22 +3171,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3295,17 +3295,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3524,22 +3524,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3758,22 +3758,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3877,22 +3877,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3957,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4472,22 +4472,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4591,22 +4591,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4837,22 +4837,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4961,17 +4961,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5075,22 +5075,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5321,22 +5321,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5912,22 +5912,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6031,22 +6031,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6155,17 +6155,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6983,22 +6983,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7098,22 +7098,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7222,17 +7222,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7336,22 +7336,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8208,32 +8208,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -8241,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8265,37 +8269,37 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8323,32 +8327,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -8356,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8380,37 +8388,37 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8479,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8510,7 +8518,7 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8525,7 +8533,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8553,32 +8561,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8586,7 +8598,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8610,37 +8622,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8668,32 +8680,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -8701,7 +8717,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8725,37 +8741,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8783,32 +8799,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8816,7 +8836,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8840,37 +8860,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8898,32 +8918,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8931,7 +8955,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8955,37 +8979,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9013,32 +9037,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -9046,7 +9074,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9070,37 +9098,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -9128,32 +9156,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9161,7 +9193,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9185,17 +9217,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9205,17 +9237,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9243,32 +9275,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9276,7 +9312,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9300,37 +9336,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9391,7 +9427,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9445,7 +9481,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -9506,7 +9542,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9621,7 +9657,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9675,7 +9711,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9736,7 +9772,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9790,7 +9826,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9887,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9905,7 +9941,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9966,7 +10002,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10020,7 +10056,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -10081,7 +10117,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10135,7 +10171,1042 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
           <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>83.8</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>87.7</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-浦东78路.xlsx
+++ b/data/export/2026-10-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1291,22 +1291,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1874,22 +1874,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2223,22 +2223,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2461,22 +2461,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3405,22 +3405,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3957,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4115,22 +4115,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5555,22 +5555,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6626,22 +6626,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7227,12 +7227,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7455,22 +7455,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7808,22 +7808,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7927,22 +7927,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8046,22 +8046,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8652,7 +8652,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8717,7 +8717,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9074,7 +9074,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9166,24 +9166,24 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9193,7 +9193,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9394,32 +9394,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9427,7 +9431,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9451,37 +9455,37 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -9542,7 +9546,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9657,7 +9661,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9696,7 +9700,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9711,7 +9715,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9739,32 +9743,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -9772,7 +9780,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9796,37 +9804,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -9854,32 +9862,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9887,7 +9899,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9911,37 +9923,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9969,32 +9981,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -10002,7 +10018,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10026,37 +10042,37 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10117,7 +10133,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10171,7 +10187,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10248,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10286,7 +10302,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10347,7 +10363,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10386,7 +10402,7 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
@@ -10401,7 +10417,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10462,7 +10478,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10516,7 +10532,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10577,7 +10593,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10616,7 +10632,7 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
@@ -10631,7 +10647,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10692,7 +10708,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10746,7 +10762,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -10807,7 +10823,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10861,7 +10877,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10938,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10976,7 +10992,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -11037,7 +11053,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11091,7 +11107,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -11152,7 +11168,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11206,7 +11222,927 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>81.6</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>85.2</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>91.8</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
           <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-浦东78路.xlsx
+++ b/data/export/2026-10-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,12 +828,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1301,12 +1301,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1526,17 +1526,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1755,17 +1755,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1994,17 +1994,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2695,22 +2695,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3176,17 +3176,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3529,17 +3529,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3758,17 +3758,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3957,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4239,17 +4239,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4472,22 +4472,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4842,17 +4842,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5080,17 +5080,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5321,17 +5321,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6274,17 +6274,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6869,17 +6869,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6988,12 +6988,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7341,17 +7341,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7455,7 +7455,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8523,17 +8523,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8642,17 +8642,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8717,7 +8717,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8756,22 +8756,22 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9074,7 +9074,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9113,17 +9113,17 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9193,7 +9193,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9356,17 +9356,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9431,7 +9431,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9780,7 +9780,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9991,24 +9991,24 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10133,7 +10133,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10248,7 +10248,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10287,7 +10287,7 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
@@ -10302,7 +10302,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10363,7 +10363,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10417,7 +10417,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10445,32 +10445,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>110分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10478,7 +10482,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10502,17 +10506,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10522,17 +10526,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10560,32 +10564,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10593,7 +10601,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10617,17 +10625,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10637,17 +10645,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10675,32 +10683,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -10708,7 +10720,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10732,37 +10744,37 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10823,7 +10835,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10877,7 +10889,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10905,32 +10917,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10938,7 +10954,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10962,17 +10978,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -10982,12 +10998,12 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -11020,32 +11036,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -11053,7 +11073,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11077,17 +11097,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11097,17 +11117,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11135,32 +11155,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -11168,7 +11192,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11192,32 +11216,32 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11283,7 +11307,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11337,7 +11361,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11398,7 +11422,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11452,7 +11476,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -11513,7 +11537,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11552,7 +11576,7 @@
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -11628,7 +11652,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11743,7 +11767,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11858,7 +11882,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11912,7 +11936,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11973,7 +11997,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12022,12 +12046,12 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -12088,7 +12112,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12132,17 +12156,477 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB99" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
-      <c r="AC99" s="2" t="inlineStr">
-        <is>
-          <t>8/18</t>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>91.8</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-浦东78路.xlsx
+++ b/data/export/2026-10-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC103"/>
+  <dimension ref="A1:AC104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10057,7 +10057,7 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11537,7 +11537,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11767,7 +11767,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11882,7 +11882,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11997,7 +11997,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="Z98" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA98" s="2" t="inlineStr">
@@ -12112,7 +12112,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12227,7 +12227,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12342,7 +12342,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12457,7 +12457,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12572,7 +12572,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12630,6 +12630,121 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-21-浦东78路.xlsx
+++ b/data/export/2026-10-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC104"/>
+  <dimension ref="A1:AC106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1296,17 +1296,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1879,17 +1879,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2113,17 +2113,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2466,17 +2466,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3176,17 +3176,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3410,17 +3410,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3957,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4001,17 +4001,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4120,17 +4120,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4725,7 +4725,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4842,17 +4842,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5441,17 +5441,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5560,17 +5560,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6512,17 +6512,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6631,17 +6631,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7460,17 +7460,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7694,17 +7694,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7813,17 +7813,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7932,12 +7932,12 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8051,17 +8051,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8408,17 +8408,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8533,7 +8533,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8642,17 +8642,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8717,7 +8717,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9009,7 +9009,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9074,7 +9074,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9431,7 +9431,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9475,17 +9475,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9705,17 +9705,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9780,7 +9780,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9824,12 +9824,12 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9943,17 +9943,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10062,17 +10062,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10187,7 +10187,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10248,7 +10248,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10287,7 +10287,7 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
@@ -10302,7 +10302,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10363,7 +10363,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10407,17 +10407,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -10601,7 +10601,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10645,17 +10645,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10720,7 +10720,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10759,7 +10759,7 @@
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10889,7 +10889,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11246,7 +11246,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -11389,32 +11389,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11422,7 +11426,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11446,17 +11450,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11466,17 +11470,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11504,32 +11508,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11537,7 +11545,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11561,17 +11569,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11581,17 +11589,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -11619,32 +11627,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -11652,7 +11664,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11676,17 +11688,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11696,12 +11708,12 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -11734,32 +11746,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11767,7 +11783,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11791,17 +11807,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11811,17 +11827,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11849,32 +11865,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11882,7 +11902,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11906,17 +11926,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11926,17 +11946,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11964,32 +11984,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -11997,7 +12021,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12021,17 +12045,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12041,17 +12065,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -12079,32 +12103,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -12112,7 +12140,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12136,17 +12164,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12156,17 +12184,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -12227,7 +12255,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12266,7 +12294,7 @@
       </c>
       <c r="Z100" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA100" s="2" t="inlineStr">
@@ -12281,7 +12309,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -12342,7 +12370,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12396,7 +12424,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -12457,7 +12485,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12496,7 +12524,7 @@
       </c>
       <c r="Z102" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA102" s="2" t="inlineStr">
@@ -12511,7 +12539,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12600,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12616,17 +12644,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -12687,7 +12715,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12731,17 +12759,247 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB104" s="2" t="inlineStr">
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
         <is>
           <t>87.0</t>
         </is>
       </c>
-      <c r="AC104" s="2" t="inlineStr">
-        <is>
-          <t>10/18</t>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-浦东78路.xlsx
+++ b/data/export/2026-10-21-浦东78路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1760,17 +1760,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2466,17 +2466,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2700,17 +2700,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3763,17 +3763,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3882,17 +3882,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4477,17 +4477,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4725,7 +4725,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5326,17 +5326,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7460,17 +7460,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8289,17 +8289,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8652,7 +8652,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8717,7 +8717,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8761,17 +8761,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9009,7 +9009,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9074,7 +9074,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9118,17 +9118,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9431,7 +9431,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9475,17 +9475,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10248,7 +10248,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10292,17 +10292,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10417,7 +10417,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10601,7 +10601,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10720,7 +10720,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10764,17 +10764,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10889,7 +10889,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11236,17 +11236,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -11545,7 +11545,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11589,17 +11589,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11837,7 +11837,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -12021,7 +12021,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12140,7 +12140,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -12222,32 +12222,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -12255,7 +12259,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12279,17 +12283,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12299,17 +12303,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -12337,32 +12341,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -12370,7 +12378,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12394,17 +12402,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12414,17 +12422,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -12452,32 +12460,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -12485,7 +12497,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12509,17 +12521,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12529,17 +12541,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -12567,32 +12579,36 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12600,7 +12616,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12624,17 +12640,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12644,17 +12660,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -12715,7 +12731,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12830,7 +12846,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12874,17 +12890,17 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -12945,7 +12961,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -12989,17 +13005,17 @@
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
